--- a/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
+++ b/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
@@ -9680,7 +9680,7 @@
 (3) Gala出発17:30はSC終了16:45の45分後で、撤収要員が不足。
 (4)Day 1全体の前倒しについて、RT・SCは短縮不可のため、日本パビリオン開会式（GOHツアー内）の所要時間次第。　(6)【9/25決定】Day 1前倒しはRTの分割で対応: RT(1) 13:00-15:00、SC 15:15-16:15、RT(2)は29日09:00-09:30（TSは09:30据え置き）。これで17:30のGala出発まで75分の余裕。COSEM（9/29合同会議）と内閣府（9/25 16:30）に提案して確定。SC時の前方席はADRC（所長が説明）と内閣府。事務局席は前方寄り（ADRC席後方）に再配置。
 (5)【9/28内閣府】10/28 16:00-16:30 MHA HQでバイ会談、16:30-16:40 MOC署名式（室長・御手洗参事官）。SC途中で退出、日本側司会は中根補佐。
-(6)【9/29 JM6】名札65枚はSCDF部署から借用（ADRCが国旗ロゴ素材と名簿〈10/13〉を提供）。当日早朝設営の可否をExpoに確認中。AV見積SGD17〜19K、カメラは演台固定1台＋U字パン1台（Sylvia案）、ADRC持込＋職員操作を提案予定。RT(1) 13:00-15:00＝Armenia〜Turkiye 22枠（各5分、Japanの直後に仙台市）、ADRC Opening 12:45-13:00＝Commissioner（tbc）・林副大臣・三浦センター長 各4分。</t>
+(6)【9/29 JM6】名札65枚はSCDF部署から借用（ADRCが国旗ロゴ素材と名簿〈10/13〉を提供）。当日早朝設営の可否をExpoに確認中。AV見積SGD17〜19K。Zoom用カメラ1台はADRC持込で決定、2台運用（演台固定＋U字パン、Sylvia案）は未決。設営開始はExpo最早08:00とSylvia（JM6、要確認）、07:30入室は未承認。RT(1) 13:00-15:00＝Armenia〜Turkiye 22枠（各5分、Japanの直後に仙台市）、ADRC Opening 12:45-13:00＝Commissioner（tbc）・林副大臣・三浦センター長 各4分。</t>
         </is>
       </c>
     </row>
@@ -14853,17 +14853,17 @@
       </c>
       <c r="C55" s="202" t="inlineStr">
         <is>
-          <t>カメラ2台と操作</t>
+          <t>カメラ（Zoom用）の持込と2台運用の可否</t>
         </is>
       </c>
       <c r="D55" s="202" t="inlineStr">
         <is>
-          <t>Sylvia案: 演台固定1台＋U字パン1台（前方中央）。10月はカメラマン確保困難。ADRC: 9/24メールどおり自前カメラ持込＋職員操作（HDMIで業者スイッチャー/Zoom PCへ）を提案。教室型1列目のRT発言者（仙台市・Google）をパンで拾えるか。</t>
+          <t>【決定】Zoom用ビデオカメラ1台はADRCが持込（仙台と同様にHDMI接続、AVオペレータへ渡す）。2台運用（演台固定＋U字パン、Sylvia 9/29案）にするかは未決。10月はカメラマン確保困難、業者機材を職員が操作する場合の損害責任をSylviaが懸念。教室型1列目のRT発言者（仙台市・Google）をどう撮るかも未決。</t>
         </is>
       </c>
       <c r="E55" s="202" t="inlineStr">
         <is>
-          <t>持込の可否、HDMI入力、見積からの減額</t>
+          <t>2台目の要否と費用、HDMI入力、見積からの減額</t>
         </is>
       </c>
       <c r="F55" s="201" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="I55" s="203" t="inlineStr">
         <is>
-          <t>未協議</t>
+          <t>協議中</t>
         </is>
       </c>
     </row>
@@ -14952,12 +14952,12 @@
       </c>
       <c r="D57" s="202" t="inlineStr">
         <is>
-          <t>前日設営はExpoが1日分課金。当日早朝の設営可否をSylviaがExpo/COSEMに確認中。</t>
+          <t>前日設営はExpoが1日分課金。JM6でSylvia「Expoに確認したところ設営開始は最早08:00」（録音83:28、要確認）。ADRCの07:30入室希望（9/24メール）は未承認。当日早朝設営の可否と開始時刻をSylviaがExpo/COSEMに確認中。</t>
         </is>
       </c>
       <c r="E57" s="202" t="inlineStr">
         <is>
-          <t>入室可能時刻（07:30）</t>
+          <t>設営開始時刻（08:00か07:30か）、29日はRT(2) 09:00開始のため準備1時間</t>
         </is>
       </c>
       <c r="F57" s="201" t="inlineStr">
@@ -15122,7 +15122,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="B62" s="77" t="inlineStr">
         <is>
@@ -15154,7 +15153,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="B67" s="77" t="inlineStr">
         <is>

--- a/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
+++ b/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D4" s="184" t="inlineStr">
         <is>
-          <t>会場準備(ステージ前方へ・テーブルマイク)／登壇者集合・接続確認</t>
+          <t>会場準備（家具は前日のまま。AV・名札のみ）／登壇者集合・接続確認</t>
         </is>
       </c>
       <c r="E4" s="95" t="n"/>
@@ -14952,12 +14952,12 @@
       </c>
       <c r="D57" s="202" t="inlineStr">
         <is>
-          <t>前日設営はExpoが1日分課金。JM6でSylvia「Expoに確認したところ設営開始は最早08:00」（録音83:28、要確認）。ADRCの07:30入室希望（9/24メール）は未承認。当日早朝設営の可否と開始時刻をSylviaがExpo/COSEMに確認中。</t>
+          <t>前日設営はExpoが1日分課金。JM6でSylvia「Expoに確認したところ設営開始は最早08:00」（録音83:28、要確認）。ADRCの07:30入室希望（9/24メール）は未承認。当日早朝設営の可否と開始時刻をSylviaがExpo/COSEMに確認中。【荒木田 9/30】机・椅子の配置を28・29日で共通にし（前方登壇者卓・演台・ステージは28日朝に設営してそのまま）、29日朝はAVと名札の準備のみとすれば08:00入室で足りる。9/24メールの「28日夜の前方組替」は不要。</t>
         </is>
       </c>
       <c r="E57" s="202" t="inlineStr">
         <is>
-          <t>設営開始時刻（08:00か07:30か）、29日はRT(2) 09:00開始のため準備1時間</t>
+          <t>設営開始時刻（08:00）、28日の前方構成を29日と同じにする可否（RT・SCでも登壇者卓を置いたまま）</t>
         </is>
       </c>
       <c r="F57" s="201" t="inlineStr">

--- a/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
+++ b/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
@@ -12416,7 +12416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="107" min="1" max="1"/>
@@ -12443,6 +12443,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="107">
       <c r="A4" s="70" t="inlineStr">
         <is>
@@ -15122,74 +15123,264 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="77" t="inlineStr">
+    <row r="61" ht="78" customHeight="1" s="107">
+      <c r="A61" s="201" t="inlineStr">
+        <is>
+          <t>J57</t>
+        </is>
+      </c>
+      <c r="B61" s="202" t="inlineStr">
+        <is>
+          <t>プログラム</t>
+        </is>
+      </c>
+      <c r="C61" s="202" t="inlineStr">
+        <is>
+          <t>ACDR Opening の持ち時間と登壇順</t>
+        </is>
+      </c>
+      <c r="D61" s="202" t="inlineStr">
+        <is>
+          <t>Sylvia 9/30（児玉経由）: Commissioner は5分、Chairman は短めに。→ 三浦 約3分・Commissioner 5分・林副大臣 4〜5分・MC 計2分（15分枠）。登壇順は暫定で三浦→Commissioner→林副大臣（後の登壇者ほど上位とするSG側プロトコルを尊重）。三浦開会挨拶は rev3（英語約340語、3分）。</t>
+        </is>
+      </c>
+      <c r="E61" s="202" t="inlineStr">
+        <is>
+          <t>登壇順の確定、Commissioner 原稿の分量（Sylvia 起案）</t>
+        </is>
+      </c>
+      <c r="F61" s="201" t="inlineStr">
+        <is>
+          <t>WhatsApp 9/30、進行シナリオ 0930 rev2</t>
+        </is>
+      </c>
+      <c r="G61" s="201" t="inlineStr">
+        <is>
+          <t>10/8</t>
+        </is>
+      </c>
+      <c r="H61" s="202" t="inlineStr">
+        <is>
+          <t>荒木田</t>
+        </is>
+      </c>
+      <c r="I61" s="203" t="inlineStr">
+        <is>
+          <t>協議中</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="78" customHeight="1" s="107">
+      <c r="A62" s="201" t="inlineStr">
+        <is>
+          <t>J58</t>
+        </is>
+      </c>
+      <c r="B62" s="202" t="inlineStr">
+        <is>
+          <t>ホスピタリティ</t>
+        </is>
+      </c>
+      <c r="C62" s="202" t="inlineStr">
+        <is>
+          <t>長官主催夕食会（10/26）</t>
+        </is>
+      </c>
+      <c r="D62" s="202" t="inlineStr">
+        <is>
+          <t>Sylvia 9/30: Home Team NS Khatib（Orchid Live Seafood）18:30。出席者は三浦・北本・宮木ほか役員（大使館表敬は27日午前に変更済）。</t>
+        </is>
+      </c>
+      <c r="E62" s="202" t="inlineStr">
+        <is>
+          <t>出席者名簿、Dorsett からの送迎</t>
+        </is>
+      </c>
+      <c r="F62" s="201" t="inlineStr">
+        <is>
+          <t>WhatsApp 9/30</t>
+        </is>
+      </c>
+      <c r="G62" s="201" t="inlineStr">
+        <is>
+          <t>10/9</t>
+        </is>
+      </c>
+      <c r="H62" s="202" t="inlineStr">
+        <is>
+          <t>児玉</t>
+        </is>
+      </c>
+      <c r="I62" s="203" t="inlineStr">
+        <is>
+          <t>協議中</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="78" customHeight="1" s="107">
+      <c r="A63" s="201" t="inlineStr">
+        <is>
+          <t>J59</t>
+        </is>
+      </c>
+      <c r="B63" s="202" t="inlineStr">
+        <is>
+          <t>事務・契約</t>
+        </is>
+      </c>
+      <c r="C63" s="202" t="inlineStr">
+        <is>
+          <t>Dorsett 客室リリースと10%アトリション</t>
+        </is>
+      </c>
+      <c r="D63" s="202" t="inlineStr">
+        <is>
+          <t>Jillian 9/30: 10%超のリリースはペナルティ（26日 30→24室: 3室分、30日 37→27室: 6室分）。契約（COSEM⇔Dorsett）: 保証ブロックは10/27〜30 各60室、S$250++/275++、2nd review 9/27「10% release of any unsold room」、「on each cut-off date」で日割り解釈の余地。26日はブロック外（追加室）。ADRC/藤中は総室泊の10%と理解、契約書は未見。</t>
+        </is>
+      </c>
+      <c r="E63" s="202" t="inlineStr">
+        <is>
+          <t>(1) 26日分はブロック外で10%規定の適用外ではないか、(2) 30日分の10%の算定基準（日別か総室泊か）、(3) ペナルティ相当分は空室で払うより利用に充てる（Hotel Mi泊の職員等を移す）、(4) 負担者（COSEM⇔ADRC）</t>
+        </is>
+      </c>
+      <c r="F63" s="201" t="inlineStr">
+        <is>
+          <t>Jillian メール 9/30、契約書画像、WhatsApp 9/30</t>
+        </is>
+      </c>
+      <c r="G63" s="201" t="inlineStr">
+        <is>
+          <t>10/3</t>
+        </is>
+      </c>
+      <c r="H63" s="202" t="inlineStr">
+        <is>
+          <t>藤中・児玉</t>
+        </is>
+      </c>
+      <c r="I63" s="203" t="inlineStr">
+        <is>
+          <t>協議中</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="78" customHeight="1" s="107">
+      <c r="A64" s="201" t="inlineStr">
+        <is>
+          <t>J60</t>
+        </is>
+      </c>
+      <c r="B64" s="202" t="inlineStr">
+        <is>
+          <t>会場・機材</t>
+        </is>
+      </c>
+      <c r="C64" s="202" t="inlineStr">
+        <is>
+          <t>会場バナーのデザイン案</t>
+        </is>
+      </c>
+      <c r="D64" s="202" t="inlineStr">
+        <is>
+          <t>Sylvia 9/30 → 荒木田に確認依頼。案: 上段 SG国旗・SCDF・COSEM・ADRC ロゴ・日本国旗、下段「SIDEX-ACDR 2026 in conjunction with FiSAC」ロゴ＋「ASIAN CONFERENCE ON DISASTER REDUCTION 2026 / 27-30 October 2026 | Singapore Expo」。会期表記はアジェンダ（27-30 Oct）と一致。内閣府ロゴ・名称なし（記者発表では内閣府が主催）→ 児玉経由で内閣府に確認。ADRC ロゴは公式データを送付。</t>
+        </is>
+      </c>
+      <c r="E64" s="202" t="inlineStr">
+        <is>
+          <t>内閣府ロゴの要否、ADRC ロゴ公式データ、寸法（卓前面布バナー／A型スタンド）</t>
+        </is>
+      </c>
+      <c r="F64" s="201" t="inlineStr">
+        <is>
+          <t>WhatsApp 9/30</t>
+        </is>
+      </c>
+      <c r="G64" s="201" t="inlineStr">
+        <is>
+          <t>10/3</t>
+        </is>
+      </c>
+      <c r="H64" s="202" t="inlineStr">
+        <is>
+          <t>荒木田・児玉</t>
+        </is>
+      </c>
+      <c r="I64" s="203" t="inlineStr">
+        <is>
+          <t>協議中</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="B66" s="77" t="inlineStr">
         <is>
           <t>凡例</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="18" t="n"/>
-      <c r="C63" s="78" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="18" t="n"/>
+      <c r="C67" s="78" t="inlineStr">
         <is>
           <t>未協議（COSEM/SCDFにまだ提示していない）</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="17" t="n"/>
-      <c r="C64" s="78" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="17" t="n"/>
+      <c r="C68" s="78" t="inlineStr">
         <is>
           <t>協議中（提示済み・回答待ち）</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="15" t="n"/>
-      <c r="C65" s="78" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="78" t="inlineStr">
         <is>
           <t>合意</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="77" t="inlineStr">
+    <row r="70"/>
+    <row r="71">
+      <c r="B71" s="77" t="inlineStr">
         <is>
           <t>集計</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="78" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="78" t="inlineStr">
         <is>
           <t>未協議</t>
         </is>
       </c>
-      <c r="C68" s="79">
-        <f>COUNTIF(I5:I60,"未協議")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="78" t="inlineStr">
+      <c r="C72" s="79">
+        <f>COUNTIF(I5:I64,"未協議")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="78" t="inlineStr">
         <is>
           <t>協議中</t>
         </is>
       </c>
-      <c r="C69" s="79">
-        <f>COUNTIF(I5:I60,"協議中")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="78" t="inlineStr">
+      <c r="C73" s="79">
+        <f>COUNTIF(I5:I64,"協議中")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="78" t="inlineStr">
         <is>
           <t>合意</t>
         </is>
       </c>
-      <c r="C70" s="79">
-        <f>COUNTIF(I5:I60,"合意")</f>
+      <c r="C74" s="79">
+        <f>COUNTIF(I5:I64,"合意")</f>
         <v/>
       </c>
     </row>

--- a/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
+++ b/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
@@ -9680,7 +9680,8 @@
 (3) Gala出発17:30はSC終了16:45の45分後で、撤収要員が不足。
 (4)Day 1全体の前倒しについて、RT・SCは短縮不可のため、日本パビリオン開会式（GOHツアー内）の所要時間次第。　(6)【9/25決定】Day 1前倒しはRTの分割で対応: RT(1) 13:00-15:00、SC 15:15-16:15、RT(2)は29日09:00-09:30（TSは09:30据え置き）。これで17:30のGala出発まで75分の余裕。COSEM（9/29合同会議）と内閣府（9/25 16:30）に提案して確定。SC時の前方席はADRC（所長が説明）と内閣府。事務局席は前方寄り（ADRC席後方）に再配置。
 (5)【9/28内閣府】10/28 16:00-16:30 MHA HQでバイ会談、16:30-16:40 MOC署名式（室長・御手洗参事官）。SC途中で退出、日本側司会は中根補佐。
-(6)【9/29 JM6】名札65枚はSCDF部署から借用（ADRCが国旗ロゴ素材と名簿〈10/13〉を提供）。当日早朝設営の可否をExpoに確認中。AV見積SGD17〜19K。Zoom用カメラ1台はADRC持込で決定、2台運用（演台固定＋U字パン、Sylvia案）は未決。設営開始はExpo最早08:00とSylvia（JM6、要確認）、07:30入室は未承認。RT(1) 13:00-15:00＝Armenia〜Turkiye 22枠（各5分、Japanの直後に仙台市）、ADRC Opening 12:45-13:00＝Commissioner（tbc）・林副大臣・三浦センター長 各4分。</t>
+(6)【9/29 JM6】名札65枚はSCDF部署から借用（ADRCが国旗ロゴ素材と名簿〈10/13〉を提供）。当日早朝設営の可否をExpoに確認中。AV見積SGD17〜19K。Zoom用カメラ1台はADRC持込で決定、2台運用（演台固定＋U字パン、Sylvia案）は未決。設営開始はExpo最早08:00とSylvia（JM6、要確認）、07:30入室は未承認。RT(1) 13:00-15:00＝Armenia〜Turkiye 22枠（各5分、Japanの直後に仙台市）、ADRC Opening 12:45-13:00＝Commissioner（tbc）・林副大臣・三浦センター長 各4分。
+(追記 9/30 児玉) 内閣府: 林副大臣は Gala 欠席（日本企業との懇親会へ）、御手洗参事官が短時間出席。副大臣は 28 日 22:20 発で帰国。ACDR Opening は英語で挨拶、肩書 Deputy Minister for Disaster Management, Cabinet Office of Japan。</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12444,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="107">
       <c r="A4" s="70" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="D61" s="202" t="inlineStr">
         <is>
-          <t>Sylvia 9/30（児玉経由）: Commissioner は5分、Chairman は短めに。→ 三浦 約3分・Commissioner 5分・林副大臣 4〜5分・MC 計2分（15分枠）。登壇順は暫定で三浦→Commissioner→林副大臣（後の登壇者ほど上位とするSG側プロトコルを尊重）。三浦開会挨拶は rev3（英語約340語、3分）。</t>
+          <t>Sylvia 9/30（児玉経由）: Commissioner は5分、Chairman は短めに。→ 三浦 約3分・Commissioner 5分・林副大臣 4〜5分・MC 計2分（15分枠）。登壇順は暫定で三浦→Commissioner→林副大臣（後の登壇者ほど上位とするSG側プロトコルを尊重）。三浦開会挨拶は rev3（英語約340語、3分）。 【9/30 内閣府確認（児玉）】林副大臣は英語で挨拶（通訳なし）、肩書 Deputy Minister for Disaster Management, Cabinet Office of Japan。</t>
         </is>
       </c>
       <c r="E61" s="202" t="inlineStr">
@@ -15282,12 +15282,12 @@
       </c>
       <c r="D64" s="202" t="inlineStr">
         <is>
-          <t>Sylvia 9/30 → 荒木田に確認依頼。案: 上段 SG国旗・SCDF・COSEM・ADRC ロゴ・日本国旗、下段「SIDEX-ACDR 2026 in conjunction with FiSAC」ロゴ＋「ASIAN CONFERENCE ON DISASTER REDUCTION 2026 / 27-30 October 2026 | Singapore Expo」。会期表記はアジェンダ（27-30 Oct）と一致。内閣府ロゴ・名称なし（記者発表では内閣府が主催）→ 児玉経由で内閣府に確認。ADRC ロゴは公式データを送付。</t>
+          <t>Sylvia 9/30 → 荒木田に確認依頼。案: 上段 SG国旗・SCDF・COSEM・ADRC ロゴ・日本国旗、下段「SIDEX-ACDR 2026 in conjunction with FiSAC」ロゴ＋「ASIAN CONFERENCE ON DISASTER REDUCTION 2026 / 27-30 October 2026 | Singapore Expo」。会期表記はアジェンダ（27-30 Oct）と一致。内閣府ロゴ・名称なし（記者発表では内閣府が主催）→ 児玉経由で内閣府に確認。ADRC ロゴは公式データを送付。 【9/30 児玉】内閣府ロゴは不要（打合せと大使館で確認済）。→ Sylvia に「デザイン了承、ADRC ロゴ高解像度データを送付」と返答。</t>
         </is>
       </c>
       <c r="E64" s="202" t="inlineStr">
         <is>
-          <t>内閣府ロゴの要否、ADRC ロゴ公式データ、寸法（卓前面布バナー／A型スタンド）</t>
+          <t>ADRC ロゴ公式データの送付、寸法（卓前面布バナー／A型スタンド）</t>
         </is>
       </c>
       <c r="F64" s="201" t="inlineStr">
@@ -15307,11 +15307,10 @@
       </c>
       <c r="I64" s="203" t="inlineStr">
         <is>
-          <t>協議中</t>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
+          <t>合意</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
       <c r="B66" s="77" t="inlineStr">
         <is>
@@ -15343,7 +15342,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="B71" s="77" t="inlineStr">
         <is>

--- a/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
+++ b/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_30_Sep_v2_93.xlsx
@@ -9074,11 +9074,6 @@
       <c r="AA9" s="94" t="n"/>
       <c r="AB9" s="94" t="n"/>
       <c r="AC9" s="95" t="n"/>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>sk_da06052da0c0227daf6db024942a34fa6f8a6428b003c6da</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="107">
       <c r="A10" s="40">
